--- a/artfynd/A 14860-2023 artfynd.xlsx
+++ b/artfynd/A 14860-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14860-2023 artfynd.xlsx
+++ b/artfynd/A 14860-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104164120</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581954.2094322823</v>
+        <v>581954</v>
       </c>
       <c r="R2" t="n">
-        <v>7010158.371507559</v>
+        <v>7010159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104164118</v>
+        <v>104164116</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581906.9915137433</v>
+        <v>581814</v>
       </c>
       <c r="R3" t="n">
-        <v>7010256.004489948</v>
+        <v>7010249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104164116</v>
+        <v>104164117</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581814.086142136</v>
+        <v>581814</v>
       </c>
       <c r="R4" t="n">
-        <v>7010248.683160655</v>
+        <v>7010249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104164119</v>
+        <v>104164115</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581954.2094322823</v>
+        <v>581814</v>
       </c>
       <c r="R5" t="n">
-        <v>7010158.371507559</v>
+        <v>7010249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104164115</v>
+        <v>104164118</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581814.086142136</v>
+        <v>581907</v>
       </c>
       <c r="R6" t="n">
-        <v>7010248.683160655</v>
+        <v>7010256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,118 +1157,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>104164117</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Hålbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>581814.086142136</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7010248.683160655</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Helgum</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14860-2023 artfynd.xlsx
+++ b/artfynd/A 14860-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164120</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164115</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104164118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>